--- a/temp/MERCADOPAGO_20250201.xlsx
+++ b/temp/MERCADOPAGO_20250201.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E395"/>
+  <dimension ref="A1:E480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10305,6 +10305,2131 @@
         </is>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>-6600</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>122999</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>-122999</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>18800</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>-18800</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>-6973</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>103505.72</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>-9177.049999999999</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Retiro de dinero</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>-95000</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>4300</v>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>-4300</v>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>36609.3</v>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>-36609.3</v>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>20900</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>-20900</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>2941390.97</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Retiro de dinero</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>-2900000</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>28200</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>-28200</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>29.72</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>264400</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>-264400</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Retiro de dinero</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>-170000</v>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Retiro de dinero</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>14400</v>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>-14400</v>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>-7500</v>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>5100</v>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>-5100</v>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Movimiento General</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>53700</v>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>-53700</v>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>-18000</v>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>69810</v>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>-69810</v>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>1103570.37</v>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>-130567.57</v>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>132000</v>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Retiro de dinero</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>-1111149.23</v>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>17676.08</v>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>270000.99</v>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>-65000</v>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>44251</v>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>-44251</v>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Retiro de dinero</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>-3025</v>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Movimiento General</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>-80000</v>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>-98096.95</v>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>8494.940000000001</v>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>-8494.940000000001</v>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>-22000</v>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>11930.81</v>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>-11930.81</v>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>750276.5699999999</v>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Retiro de dinero</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>-750000</v>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Ingreso de dinero</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Retiro de dinero</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>-42500</v>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Dinero recibido</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Rendimiento positivo de la inversión</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Movimiento General</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Mercadopago</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/temp/MERCADOPAGO_20250201.xlsx
+++ b/temp/MERCADOPAGO_20250201.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -9976,7 +9976,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11151,7 +11151,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11901,7 +11901,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Mercadopago</t>
+          <t>mercadopago</t>
         </is>
       </c>
     </row>

--- a/temp/MERCADOPAGO_20250201.xlsx
+++ b/temp/MERCADOPAGO_20250201.xlsx
@@ -471,12 +471,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-50000</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-50000,0</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>-500</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-500,0</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -521,12 +525,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>4000</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4000,0</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -546,12 +552,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>15600</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>15600,0</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -571,12 +579,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>-15600</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-15600,0</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -596,12 +606,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>42.56</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>42,56</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -621,12 +633,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>-2970</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-2970,0</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -646,12 +660,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>20.63</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20,63</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -671,12 +687,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>2454</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2454,0</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -696,12 +714,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>-2454</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-2454,0</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -721,12 +741,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>18.06</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>18,06</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -746,12 +768,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>84290</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>84290,0</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -771,12 +795,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>-77946.73</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-77946,73</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -796,12 +822,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>22.97</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>22,97</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -821,12 +849,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>5200</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5200,0</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -846,12 +876,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>-5200</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-5200,0</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -871,12 +903,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>29201.5</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>29201,5</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -896,12 +930,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>-29201.5</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-29201,5</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -921,12 +957,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>6600</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6600,0</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -946,12 +984,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>-6600</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-6600,0</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -971,12 +1011,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>22.95</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>22,95</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -996,12 +1038,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>6400</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6400,0</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1065,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>-6400</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-6400,0</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1092,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>5000</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5000,0</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1119,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>-35000</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-35000,0</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1146,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>68.84999999999999</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>68,85</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1173,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>2053539.6</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2053539,6</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1200,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>-5000</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>-5000,0</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1227,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>-510000</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-510000,0</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1254,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>-1292953.96</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>-1292953,96</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1281,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>186.94</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>186,94</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1308,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>37949.67</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>37949,67</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1335,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>-4000</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>-4000,0</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1362,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>189.21</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>189,21</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1389,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>216.94</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>216,94</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1416,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>216.01</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>216,01</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1443,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>-122845.27</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>-122845,27</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1470,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>-70000</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>-70000,0</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1497,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>40489</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>40489,0</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1524,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>-20000</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-20000,0</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1551,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>200.17</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>200,17</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1578,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>3578.02</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3578,02</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1605,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>-3200</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-3200,0</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1632,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>82.61</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>82,61</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1659,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>81.47</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>81,47</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1686,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>-80000</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-80000,0</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1713,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>4000</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4000,0</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1740,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>-4000</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>-4000,0</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1767,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>21.89</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>21,89</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1794,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>27200</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>27200,0</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1821,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>-27200</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>-27200,0</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1848,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>21.76</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>21,76</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1875,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>-3587.5</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>-3587,5</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1902,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>2400</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2400,0</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1929,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>-2400</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>-2400,0</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1956,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>9211.41</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>9211,41</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1983,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>-9211.41</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>-9211,41</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1896,12 +2010,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>47500</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>47500,0</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1921,12 +2037,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>-47500</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>-47500,0</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1946,12 +2064,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>16000</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>16000,0</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1971,12 +2091,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>-16000</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>-16000,0</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -1996,12 +2118,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v>181586</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>181586,0</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2145,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>-181586</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>-181586,0</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2046,12 +2172,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>12400</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>12400,0</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2199,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>-12400</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>-12400,0</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2226,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>56.79</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>56,79</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2121,12 +2253,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>-2860</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>-2860,0</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2146,12 +2280,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>16.83</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>16,83</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2307,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>16.85</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>16,85</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2196,12 +2334,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v>16.82</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>16,82</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2221,12 +2361,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D72" t="n">
-        <v>16.84</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>16,84</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2388,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>40000</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>40000,0</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2415,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>-40000</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>-40000,0</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2296,12 +2442,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>48200</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>48200,0</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2469,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>-48200</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>-48200,0</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2346,12 +2496,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>17600</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>17600,0</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2371,12 +2523,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>-17600</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>-17600,0</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2550,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v>249600</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>249600,0</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2577,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>-249600</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-249600,0</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2604,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v>9500</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>9500,0</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2631,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D82" t="n">
-        <v>-9500</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>-9500,0</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2496,12 +2658,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>84.43000000000001</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>84,43</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2685,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>-3237.5</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-3237,5</t>
+        </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2712,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>394706.31</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>394706,31</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2571,12 +2739,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>-115000</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>-115000,0</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2766,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v>-202362.53</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>-202362,53</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2793,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>-25000</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>-25000,0</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2646,12 +2820,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>-35000</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>-35000,0</t>
+        </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2847,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>35460</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>35460,0</t>
+        </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2874,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v>-35460</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>-35460,0</t>
+        </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2901,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>299.08</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>299,08</t>
+        </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2928,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D93" t="n">
-        <v>-4200</v>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>-4200,0</t>
+        </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2955,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>-500</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>-500,0</t>
+        </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2796,12 +2982,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D95" t="n">
-        <v>-5130</v>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>-5130,0</t>
+        </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2821,12 +3009,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D96" t="n">
-        <v>19.97</v>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>19,97</t>
+        </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2846,12 +3036,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>4330</v>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>4330,0</t>
+        </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2871,12 +3063,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>-4330</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>-4330,0</t>
+        </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2896,12 +3090,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D99" t="n">
-        <v>6200</v>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>6200,0</t>
+        </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2921,12 +3117,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D100" t="n">
-        <v>-6200</v>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>-6200,0</t>
+        </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2946,12 +3144,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>123090.42</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>123090,42</t>
+        </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2971,12 +3171,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D102" t="n">
-        <v>-120000</v>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>-120000,0</t>
+        </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -2996,12 +3198,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D103" t="n">
-        <v>120000.21</v>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>120000,21</t>
+        </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3225,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>-26000</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>-26000,0</t>
+        </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3046,12 +3252,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D105" t="n">
-        <v>97000</v>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>97000,0</t>
+        </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3279,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D106" t="n">
-        <v>-97000</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>-97000,0</t>
+        </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3096,12 +3306,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v>7584.04</v>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>7584,04</t>
+        </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3333,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>-7584.04</v>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>-7584,04</t>
+        </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3360,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>62200</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>62200,0</t>
+        </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3387,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>60.06</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>60,06</t>
+        </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3414,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D111" t="n">
-        <v>-2100</v>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>-2100,0</t>
+        </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3441,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>-77946.73</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>-77946,73</t>
+        </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3468,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D113" t="n">
-        <v>-91380</v>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>-91380,0</t>
+        </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3271,12 +3495,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D114" t="n">
-        <v>1714114.13</v>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1714114,13</t>
+        </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3296,12 +3522,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D115" t="n">
-        <v>-1017785.25</v>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>-1017785,25</t>
+        </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3321,12 +3549,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D116" t="n">
-        <v>-510000</v>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>-510000,0</t>
+        </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3576,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D117" t="n">
-        <v>29644.23</v>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>29644,23</t>
+        </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3371,12 +3603,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D118" t="n">
-        <v>144.13</v>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>144,13</t>
+        </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3396,12 +3630,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D119" t="n">
-        <v>-4500</v>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>-4500,0</t>
+        </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3657,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D120" t="n">
-        <v>161.73</v>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>161,73</t>
+        </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3684,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D121" t="n">
-        <v>180000</v>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>180000,0</t>
+        </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3711,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D122" t="n">
-        <v>-180000</v>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>-180000,0</t>
+        </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3496,12 +3738,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D123" t="n">
-        <v>-3000</v>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>-3000,0</t>
+        </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3521,12 +3765,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D124" t="n">
-        <v>161.46</v>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>161,46</t>
+        </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3546,12 +3792,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D125" t="n">
-        <v>162.87</v>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>162,87</t>
+        </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3819,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D126" t="n">
-        <v>3700</v>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3700,0</t>
+        </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3846,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D127" t="n">
-        <v>-3700</v>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>-3700,0</t>
+        </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3621,12 +3873,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D128" t="n">
-        <v>-70000</v>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>-70000,0</t>
+        </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3900,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D129" t="n">
-        <v>-70029.7</v>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>-70029,7</t>
+        </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3927,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D130" t="n">
-        <v>5655.61</v>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>5655,61</t>
+        </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3696,12 +3954,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D131" t="n">
-        <v>129564</v>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>129564,0</t>
+        </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3721,12 +3981,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D132" t="n">
-        <v>-22000</v>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>-22000,0</t>
+        </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3746,12 +4008,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D133" t="n">
-        <v>183.9</v>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>183,9</t>
+        </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3771,12 +4035,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D134" t="n">
-        <v>-1975</v>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>-1975,0</t>
+        </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3796,12 +4062,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D135" t="n">
-        <v>-20000</v>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>-20000,0</t>
+        </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3821,12 +4089,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D136" t="n">
-        <v>140.35</v>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>140,35</t>
+        </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3846,12 +4116,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D137" t="n">
-        <v>126.57</v>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>126,57</t>
+        </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3871,12 +4143,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D138" t="n">
-        <v>327384.51</v>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>327384,51</t>
+        </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3896,12 +4170,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D139" t="n">
-        <v>-400000</v>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>-400000,0</t>
+        </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3921,12 +4197,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D140" t="n">
-        <v>11400</v>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>11400,0</t>
+        </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3946,12 +4224,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D141" t="n">
-        <v>-11400</v>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>-11400,0</t>
+        </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3971,12 +4251,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D142" t="n">
-        <v>74.58</v>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>74,58</t>
+        </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -3996,12 +4278,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D143" t="n">
-        <v>27399.06</v>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>27399,06</t>
+        </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4305,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D144" t="n">
-        <v>-27399.06</v>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>-27399,06</t>
+        </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4332,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D145" t="n">
-        <v>2000</v>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2000,0</t>
+        </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4359,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D146" t="n">
-        <v>-2000</v>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>-2000,0</t>
+        </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4096,12 +4386,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D147" t="n">
-        <v>74.92</v>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>74,92</t>
+        </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4121,12 +4413,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D148" t="n">
-        <v>26517.96</v>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>26517,96</t>
+        </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4440,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D149" t="n">
-        <v>-26517.96</v>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>-26517,96</t>
+        </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4171,12 +4467,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D150" t="n">
-        <v>14450</v>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>14450,0</t>
+        </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4196,12 +4494,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D151" t="n">
-        <v>-14450</v>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>-14450,0</t>
+        </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4521,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D152" t="n">
-        <v>6100</v>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>6100,0</t>
+        </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4246,12 +4548,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D153" t="n">
-        <v>-6100</v>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>-6100,0</t>
+        </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4575,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D154" t="n">
-        <v>9500</v>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>9500,0</t>
+        </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4296,12 +4602,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D155" t="n">
-        <v>-9500</v>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>-9500,0</t>
+        </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4321,12 +4629,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D156" t="n">
-        <v>301.2</v>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>301,2</t>
+        </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4656,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D157" t="n">
-        <v>26400</v>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>26400,0</t>
+        </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4683,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D158" t="n">
-        <v>-26400</v>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-26400,0</t>
+        </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4710,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D159" t="n">
-        <v>2280</v>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2280,0</t>
+        </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4421,12 +4737,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D160" t="n">
-        <v>-2280</v>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>-2280,0</t>
+        </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4446,12 +4764,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D161" t="n">
-        <v>75.52</v>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>75,52</t>
+        </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4791,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D162" t="n">
-        <v>39400</v>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>39400,0</t>
+        </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4818,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D163" t="n">
-        <v>-39400</v>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>-39400,0</t>
+        </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4521,12 +4845,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D164" t="n">
-        <v>1200</v>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1200,0</t>
+        </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4546,12 +4872,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D165" t="n">
-        <v>75.58</v>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>75,58</t>
+        </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4571,12 +4899,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D166" t="n">
-        <v>4000</v>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>4000,0</t>
+        </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4926,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D167" t="n">
-        <v>-4000</v>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>-4000,0</t>
+        </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4621,12 +4953,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D168" t="n">
-        <v>76.48</v>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>76,48</t>
+        </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4646,12 +4980,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D169" t="n">
-        <v>9500</v>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>9500,0</t>
+        </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4671,12 +5007,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D170" t="n">
-        <v>-9500</v>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>-9500,0</t>
+        </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4696,12 +5034,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D171" t="n">
-        <v>230.03</v>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>230,03</t>
+        </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4721,12 +5061,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D172" t="n">
-        <v>238793.65</v>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>238793,65</t>
+        </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4746,12 +5088,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D173" t="n">
-        <v>10000</v>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>10000,0</t>
+        </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4771,12 +5115,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D174" t="n">
-        <v>-353669.19</v>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>-353669,19</t>
+        </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4796,12 +5142,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D175" t="n">
-        <v>250.12</v>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>250,12</t>
+        </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4821,12 +5169,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D176" t="n">
-        <v>15500</v>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>15500,0</t>
+        </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4846,12 +5196,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D177" t="n">
-        <v>-15500</v>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>-15500,0</t>
+        </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4871,12 +5223,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D178" t="n">
-        <v>2900</v>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2900,0</t>
+        </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4896,12 +5250,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D179" t="n">
-        <v>-2900</v>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>-2900,0</t>
+        </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4921,12 +5277,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D180" t="n">
-        <v>1.67</v>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4946,12 +5304,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D181" t="n">
-        <v>0.83</v>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0,83</t>
+        </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4971,12 +5331,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D182" t="n">
-        <v>2129768.65</v>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2129768,65</t>
+        </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -4996,12 +5358,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D183" t="n">
-        <v>-2119217.32</v>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-2119217,32</t>
+        </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5021,12 +5385,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D184" t="n">
-        <v>121569</v>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>121569,0</t>
+        </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5046,12 +5412,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D185" t="n">
-        <v>-121569</v>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>-121569,0</t>
+        </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5439,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D186" t="n">
-        <v>8993.959999999999</v>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>8993,96</t>
+        </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5096,12 +5466,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D187" t="n">
-        <v>-8993.959999999999</v>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>-8993,96</t>
+        </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5121,12 +5493,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D188" t="n">
-        <v>25.81</v>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>25,81</t>
+        </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5146,12 +5520,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D189" t="n">
-        <v>8.57</v>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>8,57</t>
+        </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5171,12 +5547,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D190" t="n">
-        <v>61724.82</v>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>61724,82</t>
+        </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5574,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D191" t="n">
-        <v>53.7</v>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>53,7</t>
+        </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5221,12 +5601,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D192" t="n">
-        <v>25620</v>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>25620,0</t>
+        </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5628,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D193" t="n">
-        <v>-25620</v>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>-25620,0</t>
+        </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5271,12 +5655,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D194" t="n">
-        <v>54.1</v>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>54,1</t>
+        </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5682,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D195" t="n">
-        <v>249600</v>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>249600,0</t>
+        </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5321,12 +5709,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D196" t="n">
-        <v>-249600</v>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>-249600,0</t>
+        </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5346,12 +5736,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D197" t="n">
-        <v>613461.83</v>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>613461,83</t>
+        </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5763,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D198" t="n">
-        <v>-35000</v>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>-35000,0</t>
+        </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5790,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D199" t="n">
-        <v>-510000</v>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>-510000,0</t>
+        </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5421,12 +5817,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D200" t="n">
-        <v>-16000</v>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>-16000,0</t>
+        </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5446,12 +5844,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D201" t="n">
-        <v>-16100</v>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>-16100,0</t>
+        </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5471,12 +5871,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D202" t="n">
-        <v>82.81</v>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>82,81</t>
+        </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5496,12 +5898,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D203" t="n">
-        <v>43976.4</v>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>43976,4</t>
+        </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5521,12 +5925,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D204" t="n">
-        <v>-43976.4</v>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>-43976,4</t>
+        </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5546,12 +5952,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D205" t="n">
-        <v>5100</v>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>5100,0</t>
+        </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5571,12 +5979,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D206" t="n">
-        <v>-5100</v>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>-5100,0</t>
+        </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5596,12 +6006,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D207" t="n">
-        <v>-5000</v>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>-5000,0</t>
+        </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5621,12 +6033,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D208" t="n">
-        <v>274.77</v>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>274,77</t>
+        </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5646,12 +6060,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D209" t="n">
-        <v>17735.5</v>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>17735,5</t>
+        </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5671,12 +6087,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D210" t="n">
-        <v>-17735.5</v>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>-17735,5</t>
+        </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5696,12 +6114,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D211" t="n">
-        <v>-89952.53</v>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>-89952,53</t>
+        </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5721,12 +6141,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D212" t="n">
-        <v>91.54000000000001</v>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>91,54</t>
+        </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5746,12 +6168,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D213" t="n">
-        <v>68819.38</v>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>68819,38</t>
+        </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5771,12 +6195,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D214" t="n">
-        <v>-77946.73</v>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>-77946,73</t>
+        </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5796,12 +6222,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D215" t="n">
-        <v>5.37</v>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>5,37</t>
+        </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5821,12 +6249,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D216" t="n">
-        <v>7136</v>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>7136,0</t>
+        </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5846,12 +6276,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D217" t="n">
-        <v>-7136</v>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>-7136,0</t>
+        </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5871,12 +6303,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D218" t="n">
-        <v>37400</v>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>37400,0</t>
+        </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5896,12 +6330,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D219" t="n">
-        <v>-37400</v>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>-37400,0</t>
+        </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5921,12 +6357,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D220" t="n">
-        <v>25.74</v>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>25,74</t>
+        </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5946,12 +6384,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D221" t="n">
-        <v>1350783.64</v>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>1350783,64</t>
+        </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5971,12 +6411,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D222" t="n">
-        <v>-1077694.43</v>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>-1077694,43</t>
+        </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -5996,12 +6438,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D223" t="n">
-        <v>-45000</v>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>-45000,0</t>
+        </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6465,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D224" t="n">
-        <v>-53917.1</v>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>-53917,1</t>
+        </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6046,12 +6492,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D225" t="n">
-        <v>182.98</v>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>182,98</t>
+        </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6071,12 +6519,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D226" t="n">
-        <v>175000</v>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>175000,0</t>
+        </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6546,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D227" t="n">
-        <v>-175000</v>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>-175000,0</t>
+        </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6121,12 +6573,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D228" t="n">
-        <v>136.96</v>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>136,96</t>
+        </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6600,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D229" t="n">
-        <v>34894.91</v>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>34894,91</t>
+        </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6171,12 +6627,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D230" t="n">
-        <v>179985</v>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>179985,0</t>
+        </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6196,12 +6654,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D231" t="n">
-        <v>-300000</v>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>-300000,0</t>
+        </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6221,12 +6681,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D232" t="n">
-        <v>72.3</v>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>72,3</t>
+        </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6246,12 +6708,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D233" t="n">
-        <v>237.47</v>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>237,47</t>
+        </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6271,12 +6735,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D234" t="n">
-        <v>-237.47</v>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-237,47</t>
+        </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6296,12 +6762,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D235" t="n">
-        <v>-13071.26</v>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>-13071,26</t>
+        </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6321,12 +6789,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D236" t="n">
-        <v>1827187.41</v>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>1827187,41</t>
+        </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6816,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D237" t="n">
-        <v>11900</v>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>11900,0</t>
+        </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6371,12 +6843,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D238" t="n">
-        <v>-11900</v>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>-11900,0</t>
+        </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6396,12 +6870,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D239" t="n">
-        <v>-1827187.41</v>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-1827187,41</t>
+        </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6897,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D240" t="n">
-        <v>55000</v>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>55000,0</t>
+        </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6446,12 +6924,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D241" t="n">
-        <v>-55000</v>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>-55000,0</t>
+        </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6471,12 +6951,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D242" t="n">
-        <v>63.08</v>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>63,08</t>
+        </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6496,12 +6978,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D243" t="n">
-        <v>70153.97</v>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>70153,97</t>
+        </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6521,12 +7005,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D244" t="n">
-        <v>-70153.97</v>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>-70153,97</t>
+        </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6546,12 +7032,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D245" t="n">
-        <v>15670</v>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>15670,0</t>
+        </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6571,12 +7059,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D246" t="n">
-        <v>-15670</v>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>-15670,0</t>
+        </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6596,12 +7086,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D247" t="n">
-        <v>-44500</v>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>-44500,0</t>
+        </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6621,12 +7113,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D248" t="n">
-        <v>190.75</v>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>190,75</t>
+        </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6646,12 +7140,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D249" t="n">
-        <v>28.91</v>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>28,91</t>
+        </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6671,12 +7167,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D250" t="n">
-        <v>28.95</v>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>28,95</t>
+        </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6696,12 +7194,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D251" t="n">
-        <v>10000</v>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>10000,0</t>
+        </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6721,12 +7221,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D252" t="n">
-        <v>118000</v>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>118000,0</t>
+        </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6746,12 +7248,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D253" t="n">
-        <v>-118000</v>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>-118000,0</t>
+        </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6771,12 +7275,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D254" t="n">
-        <v>68000</v>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>68000,0</t>
+        </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6796,12 +7302,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D255" t="n">
-        <v>-5000</v>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>-5000,0</t>
+        </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6821,12 +7329,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D256" t="n">
-        <v>19500</v>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>19500,0</t>
+        </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6846,12 +7356,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D257" t="n">
-        <v>4635</v>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>4635,0</t>
+        </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6871,12 +7383,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D258" t="n">
-        <v>-4635</v>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>-4635,0</t>
+        </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6896,12 +7410,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D259" t="n">
-        <v>142.74</v>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>142,74</t>
+        </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6921,12 +7437,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D260" t="n">
-        <v>134306.41</v>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>134306,41</t>
+        </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6946,12 +7464,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D261" t="n">
-        <v>100000</v>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>100000,0</t>
+        </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6971,12 +7491,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D262" t="n">
-        <v>-278971.23</v>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>-278971,23</t>
+        </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -6996,12 +7518,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D263" t="n">
-        <v>62.61</v>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>62,61</t>
+        </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7545,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D264" t="n">
-        <v>785172.09</v>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>785172,09</t>
+        </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7046,12 +7572,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D265" t="n">
-        <v>-550000</v>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>-550000,0</t>
+        </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7071,12 +7599,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D266" t="n">
-        <v>-200000</v>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>-200000,0</t>
+        </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7096,12 +7626,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D267" t="n">
-        <v>29500</v>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>29500,0</t>
+        </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7653,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D268" t="n">
-        <v>-29500</v>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>-29500,0</t>
+        </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7680,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D269" t="n">
-        <v>11028</v>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>11028,0</t>
+        </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7171,12 +7707,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D270" t="n">
-        <v>-11028</v>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>-11028,0</t>
+        </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7196,12 +7734,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D271" t="n">
-        <v>87.84999999999999</v>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>87,85</t>
+        </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7221,12 +7761,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D272" t="n">
-        <v>87.92</v>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>87,92</t>
+        </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7246,12 +7788,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D273" t="n">
-        <v>264400</v>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>264400,0</t>
+        </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7815,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D274" t="n">
-        <v>-264400</v>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>-264400,0</t>
+        </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7296,12 +7842,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D275" t="n">
-        <v>88.45</v>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>88,45</t>
+        </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7321,12 +7869,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D276" t="n">
-        <v>1397915.73</v>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>1397915,73</t>
+        </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7346,12 +7896,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D277" t="n">
-        <v>-35000</v>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>-35000,0</t>
+        </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7923,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D278" t="n">
-        <v>-25000</v>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>-25000,0</t>
+        </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7396,12 +7950,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D279" t="n">
-        <v>-1323685.52</v>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-1323685,52</t>
+        </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7421,12 +7977,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D280" t="n">
-        <v>10000</v>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>10000,0</t>
+        </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7446,12 +8004,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D281" t="n">
-        <v>-10000</v>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>-10000,0</t>
+        </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7471,12 +8031,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D282" t="n">
-        <v>39574.32</v>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>39574,32</t>
+        </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7496,12 +8058,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D283" t="n">
-        <v>-7600</v>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>-7600,0</t>
+        </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7521,12 +8085,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D284" t="n">
-        <v>13500</v>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>13500,0</t>
+        </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7546,12 +8112,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D285" t="n">
-        <v>-13500</v>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>-13500,0</t>
+        </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7571,12 +8139,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D286" t="n">
-        <v>297.84</v>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>297,84</t>
+        </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7596,12 +8166,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D287" t="n">
-        <v>123.33</v>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>123,33</t>
+        </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7621,12 +8193,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D288" t="n">
-        <v>11408.63</v>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>11408,63</t>
+        </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7646,12 +8220,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D289" t="n">
-        <v>-11408.63</v>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>-11408,63</t>
+        </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7671,12 +8247,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D290" t="n">
-        <v>-18000</v>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>-18000,0</t>
+        </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7696,12 +8274,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D291" t="n">
-        <v>-30250</v>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>-30250,0</t>
+        </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7721,12 +8301,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D292" t="n">
-        <v>-35000</v>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>-35000,0</t>
+        </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7746,12 +8328,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D293" t="n">
-        <v>25677.6</v>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>25677,6</t>
+        </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7771,12 +8355,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D294" t="n">
-        <v>-1677.6</v>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>-1677,6</t>
+        </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7796,12 +8382,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D295" t="n">
-        <v>-24000</v>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>-24000,0</t>
+        </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7821,12 +8409,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D296" t="n">
-        <v>2700</v>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2700,0</t>
+        </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7846,12 +8436,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D297" t="n">
-        <v>-2700</v>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>-2700,0</t>
+        </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7871,12 +8463,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D298" t="n">
-        <v>88.55</v>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>88,55</t>
+        </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7896,12 +8490,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D299" t="n">
-        <v>7200</v>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>7200,0</t>
+        </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7921,12 +8517,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D300" t="n">
-        <v>-7200</v>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-7200,0</t>
+        </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7946,12 +8544,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D301" t="n">
-        <v>-4050</v>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>-4050,0</t>
+        </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7971,12 +8571,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D302" t="n">
-        <v>59.69</v>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>59,69</t>
+        </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -7996,12 +8598,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D303" t="n">
-        <v>2389319.22</v>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2389319,22</t>
+        </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8625,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D304" t="n">
-        <v>-2046961.62</v>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>-2046961,62</t>
+        </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8046,12 +8652,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D305" t="n">
-        <v>-26000</v>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>-26000,0</t>
+        </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8071,12 +8679,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D306" t="n">
-        <v>312.35</v>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>312,35</t>
+        </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8096,12 +8706,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D307" t="n">
-        <v>-90072.88</v>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>-90072,88</t>
+        </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8121,12 +8733,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D308" t="n">
-        <v>-77946.73</v>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>-77946,73</t>
+        </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8146,12 +8760,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D309" t="n">
-        <v>-21500</v>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>-21500,0</t>
+        </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8171,12 +8787,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D310" t="n">
-        <v>-10000</v>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>-10000,0</t>
+        </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8196,12 +8814,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D311" t="n">
-        <v>61314.58</v>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>61314,58</t>
+        </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8221,12 +8841,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D312" t="n">
-        <v>-58000</v>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>-58000,0</t>
+        </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8246,12 +8868,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D313" t="n">
-        <v>11300</v>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>11300,0</t>
+        </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8271,12 +8895,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D314" t="n">
-        <v>-11300</v>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>-11300,0</t>
+        </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8296,12 +8922,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D315" t="n">
-        <v>503.47</v>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>503,47</t>
+        </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8949,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D316" t="n">
-        <v>143.69</v>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>143,69</t>
+        </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8976,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D317" t="n">
-        <v>142.97</v>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>142,97</t>
+        </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8371,12 +9003,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D318" t="n">
-        <v>143.12</v>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>143,12</t>
+        </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8396,12 +9030,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D319" t="n">
-        <v>143.11</v>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>143,11</t>
+        </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8421,12 +9057,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D320" t="n">
-        <v>-16000</v>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-16000,0</t>
+        </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8446,12 +9084,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D321" t="n">
-        <v>20000</v>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>20000,0</t>
+        </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8471,12 +9111,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D322" t="n">
-        <v>-50000</v>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-50000,0</t>
+        </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8496,12 +9138,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D323" t="n">
-        <v>1760</v>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>1760,0</t>
+        </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8521,12 +9165,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D324" t="n">
-        <v>-1760</v>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>-1760,0</t>
+        </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8546,12 +9192,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D325" t="n">
-        <v>-17000</v>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-17000,0</t>
+        </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8571,12 +9219,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D326" t="n">
-        <v>9745.43</v>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>9745,43</t>
+        </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8596,12 +9246,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D327" t="n">
-        <v>429.83</v>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>429,83</t>
+        </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8621,12 +9273,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D328" t="n">
-        <v>100000</v>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>100000,0</t>
+        </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8646,12 +9300,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D329" t="n">
-        <v>-61947.04</v>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-61947,04</t>
+        </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8671,12 +9327,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D330" t="n">
-        <v>-122348.29</v>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-122348,29</t>
+        </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8696,12 +9354,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D331" t="n">
-        <v>175.08</v>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>175,08</t>
+        </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8721,12 +9381,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D332" t="n">
-        <v>-194.9</v>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-194,9</t>
+        </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8746,12 +9408,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D333" t="n">
-        <v>46.25</v>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>46,25</t>
+        </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8771,12 +9435,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D334" t="n">
-        <v>46.16</v>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>46,16</t>
+        </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8796,12 +9462,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D335" t="n">
-        <v>46.06</v>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>46,06</t>
+        </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8821,12 +9489,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D336" t="n">
-        <v>2045209.84</v>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2045209,84</t>
+        </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8846,12 +9516,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D337" t="n">
-        <v>-950000</v>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>-950000,0</t>
+        </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8871,12 +9543,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D338" t="n">
-        <v>-700000</v>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-700000,0</t>
+        </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8896,12 +9570,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D339" t="n">
-        <v>-29000</v>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-29000,0</t>
+        </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8921,12 +9597,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D340" t="n">
-        <v>9272.030000000001</v>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>9272,03</t>
+        </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8946,12 +9624,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D341" t="n">
-        <v>-9272.030000000001</v>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-9272,03</t>
+        </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8971,12 +9651,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D342" t="n">
-        <v>966.45</v>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>966,45</t>
+        </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -8996,12 +9678,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D343" t="n">
-        <v>-330000</v>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-330000,0</t>
+        </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9021,12 +9705,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D344" t="n">
-        <v>71.98999999999999</v>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>71,99</t>
+        </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9046,12 +9732,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D345" t="n">
-        <v>72.17</v>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>72,17</t>
+        </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9071,12 +9759,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D346" t="n">
-        <v>71.92</v>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>71,92</t>
+        </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9096,12 +9786,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D347" t="n">
-        <v>72.26000000000001</v>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>72,26</t>
+        </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9121,12 +9813,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D348" t="n">
-        <v>32199</v>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>32199,0</t>
+        </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9146,12 +9840,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D349" t="n">
-        <v>-32199</v>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-32199,0</t>
+        </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9171,12 +9867,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D350" t="n">
-        <v>264400</v>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>264400,0</t>
+        </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9196,12 +9894,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D351" t="n">
-        <v>-264400</v>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-264400,0</t>
+        </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9221,12 +9921,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D352" t="n">
-        <v>21274.69</v>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>21274,69</t>
+        </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9246,12 +9948,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D353" t="n">
-        <v>-21274.69</v>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-21274,69</t>
+        </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9271,12 +9975,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D354" t="n">
-        <v>-65000</v>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-65000,0</t>
+        </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9296,12 +10002,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D355" t="n">
-        <v>13479.26</v>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>13479,26</t>
+        </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9321,12 +10029,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D356" t="n">
-        <v>24145</v>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>24145,0</t>
+        </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9346,12 +10056,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D357" t="n">
-        <v>-24145</v>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-24145,0</t>
+        </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9371,12 +10083,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D358" t="n">
-        <v>2060</v>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2060,0</t>
+        </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9396,12 +10110,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D359" t="n">
-        <v>-2060</v>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-2060,0</t>
+        </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9421,12 +10137,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D360" t="n">
-        <v>220.55</v>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>220,55</t>
+        </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9446,12 +10164,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D361" t="n">
-        <v>683370.05</v>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>683370,05</t>
+        </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9471,12 +10191,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D362" t="n">
-        <v>-650000</v>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-650000,0</t>
+        </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9496,12 +10218,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D363" t="n">
-        <v>61.03</v>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>61,03</t>
+        </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9521,12 +10245,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D364" t="n">
-        <v>-25000</v>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>-25000,0</t>
+        </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9546,12 +10272,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D365" t="n">
-        <v>-35000</v>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>-35000,0</t>
+        </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9571,12 +10299,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D366" t="n">
-        <v>102316.73</v>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>102316,73</t>
+        </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9596,12 +10326,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D367" t="n">
-        <v>-98096.95</v>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>-98096,95</t>
+        </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9621,12 +10353,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D368" t="n">
-        <v>3553.53</v>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>3553,53</t>
+        </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9646,12 +10380,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D369" t="n">
-        <v>160446</v>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>160446,0</t>
+        </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9671,12 +10407,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D370" t="n">
-        <v>-164000</v>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>-164000,0</t>
+        </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9696,12 +10434,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D371" t="n">
-        <v>21.53</v>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>21,53</t>
+        </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9721,12 +10461,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D372" t="n">
-        <v>-6000</v>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>-6000,0</t>
+        </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9746,12 +10488,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D373" t="n">
-        <v>22.27</v>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>22,27</t>
+        </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9771,12 +10515,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D374" t="n">
-        <v>100000</v>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>100000,0</t>
+        </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9796,12 +10542,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D375" t="n">
-        <v>-2148</v>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>-2148,0</t>
+        </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9821,12 +10569,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D376" t="n">
-        <v>-100000</v>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-100000,0</t>
+        </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9846,12 +10596,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D377" t="n">
-        <v>17.91</v>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>17,91</t>
+        </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9871,12 +10623,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D378" t="n">
-        <v>-20900</v>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-20900,0</t>
+        </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9896,12 +10650,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D379" t="n">
-        <v>250000</v>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>250000,0</t>
+        </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9921,12 +10677,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D380" t="n">
-        <v>-221882.46</v>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-221882,46</t>
+        </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9946,12 +10704,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D381" t="n">
-        <v>45000</v>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>45000,0</t>
+        </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9971,12 +10731,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D382" t="n">
-        <v>103000</v>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>103000,0</t>
+        </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -9996,12 +10758,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D383" t="n">
-        <v>-158510.43</v>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-158510,43</t>
+        </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10021,12 +10785,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D384" t="n">
-        <v>64761.72</v>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>64761,72</t>
+        </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10046,12 +10812,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D385" t="n">
-        <v>-64761.72</v>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-64761,72</t>
+        </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10071,12 +10839,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D386" t="n">
-        <v>363.69</v>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>363,69</t>
+        </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10096,12 +10866,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D387" t="n">
-        <v>311469.49</v>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>311469,49</t>
+        </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10121,12 +10893,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D388" t="n">
-        <v>-186127.06</v>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-186127,06</t>
+        </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10146,12 +10920,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D389" t="n">
-        <v>-100000</v>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-100000,0</t>
+        </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10947,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D390" t="n">
-        <v>5421.18</v>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>5421,18</t>
+        </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10196,12 +10974,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D391" t="n">
-        <v>-1060</v>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>-1060,0</t>
+        </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10221,12 +11001,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D392" t="n">
-        <v>-40000</v>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>-40000,0</t>
+        </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10246,12 +11028,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D393" t="n">
-        <v>37.47</v>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>37,47</t>
+        </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10271,12 +11055,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D394" t="n">
-        <v>18000</v>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>18000,0</t>
+        </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10296,12 +11082,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D395" t="n">
-        <v>-18000</v>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>-18000,0</t>
+        </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10321,12 +11109,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D396" t="n">
-        <v>6.57</v>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>6,57</t>
+        </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10346,12 +11136,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D397" t="n">
-        <v>6600</v>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>6600,0</t>
+        </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10371,12 +11163,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D398" t="n">
-        <v>-6600</v>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>-6600,0</t>
+        </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10396,12 +11190,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D399" t="n">
-        <v>122999</v>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>122999,0</t>
+        </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10421,12 +11217,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D400" t="n">
-        <v>-122999</v>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>-122999,0</t>
+        </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10446,12 +11244,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D401" t="n">
-        <v>18800</v>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>18800,0</t>
+        </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10471,12 +11271,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D402" t="n">
-        <v>-18800</v>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>-18800,0</t>
+        </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10496,12 +11298,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D403" t="n">
-        <v>25.03</v>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>25,03</t>
+        </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10521,12 +11325,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D404" t="n">
-        <v>-6973</v>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>-6973,0</t>
+        </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10546,12 +11352,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D405" t="n">
-        <v>6.3</v>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>6,3</t>
+        </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10571,12 +11379,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D406" t="n">
-        <v>1.18</v>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>1,18</t>
+        </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10596,12 +11406,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D407" t="n">
-        <v>12000</v>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>12000,0</t>
+        </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10621,12 +11433,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D408" t="n">
-        <v>-12000</v>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-12000,0</t>
+        </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10646,12 +11460,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D409" t="n">
-        <v>1.19</v>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>1,19</t>
+        </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10671,12 +11487,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D410" t="n">
-        <v>1.19</v>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>1,19</t>
+        </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10696,12 +11514,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D411" t="n">
-        <v>103505.72</v>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>103505,72</t>
+        </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10721,12 +11541,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D412" t="n">
-        <v>-9177.049999999999</v>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>-9177,05</t>
+        </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10746,12 +11568,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D413" t="n">
-        <v>-95000</v>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-95000,0</t>
+        </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10771,12 +11595,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D414" t="n">
-        <v>4300</v>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>4300,0</t>
+        </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10796,12 +11622,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D415" t="n">
-        <v>-4300</v>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-4300,0</t>
+        </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10821,12 +11649,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D416" t="n">
-        <v>36609.3</v>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>36609,3</t>
+        </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10846,12 +11676,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D417" t="n">
-        <v>-36609.3</v>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-36609,3</t>
+        </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10871,12 +11703,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D418" t="n">
-        <v>20900</v>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>20900,0</t>
+        </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10896,12 +11730,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D419" t="n">
-        <v>-20900</v>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-20900,0</t>
+        </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10921,12 +11757,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D420" t="n">
-        <v>3.58</v>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>3,58</t>
+        </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10946,12 +11784,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D421" t="n">
-        <v>0.68</v>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>0,68</t>
+        </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10971,12 +11811,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D422" t="n">
-        <v>2941390.97</v>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2941390,97</t>
+        </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -10996,12 +11838,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D423" t="n">
-        <v>-2900000</v>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-2900000,0</t>
+        </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11021,12 +11865,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D424" t="n">
-        <v>28200</v>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>28200,0</t>
+        </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11046,12 +11892,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D425" t="n">
-        <v>-28200</v>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-28200,0</t>
+        </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11071,12 +11919,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D426" t="n">
-        <v>29.72</v>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>29,72</t>
+        </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11096,12 +11946,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D427" t="n">
-        <v>264400</v>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>264400,0</t>
+        </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11121,12 +11973,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D428" t="n">
-        <v>-264400</v>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-264400,0</t>
+        </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11146,12 +12000,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D429" t="n">
-        <v>200000</v>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>200000,0</t>
+        </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11171,12 +12027,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D430" t="n">
-        <v>-200</v>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-200,0</t>
+        </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11196,12 +12054,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D431" t="n">
-        <v>-170000</v>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-170000,0</t>
+        </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11221,12 +12081,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D432" t="n">
-        <v>-30000</v>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-30000,0</t>
+        </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11246,12 +12108,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D433" t="n">
-        <v>-200</v>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-200,0</t>
+        </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11271,12 +12135,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D434" t="n">
-        <v>29.03</v>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>29,03</t>
+        </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11296,12 +12162,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D435" t="n">
-        <v>-6000</v>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-6000,0</t>
+        </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11321,12 +12189,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D436" t="n">
-        <v>24.05</v>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>24,05</t>
+        </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11346,12 +12216,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D437" t="n">
-        <v>100000</v>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>100000,0</t>
+        </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11371,12 +12243,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D438" t="n">
-        <v>14400</v>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>14400,0</t>
+        </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11396,12 +12270,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D439" t="n">
-        <v>-14400</v>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-14400,0</t>
+        </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11421,12 +12297,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D440" t="n">
-        <v>-100000</v>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-100000,0</t>
+        </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11446,12 +12324,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D441" t="n">
-        <v>7500</v>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>7500,0</t>
+        </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11471,12 +12351,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D442" t="n">
-        <v>-7500</v>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-7500,0</t>
+        </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11496,12 +12378,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D443" t="n">
-        <v>5100</v>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>5100,0</t>
+        </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11521,12 +12405,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D444" t="n">
-        <v>-5100</v>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-5100,0</t>
+        </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11546,12 +12432,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D445" t="n">
-        <v>-25000</v>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-25000,0</t>
+        </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11571,12 +12459,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D446" t="n">
-        <v>53700</v>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>53700,0</t>
+        </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11596,12 +12486,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D447" t="n">
-        <v>-53700</v>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-53700,0</t>
+        </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11621,12 +12513,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D448" t="n">
-        <v>18000</v>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>18000,0</t>
+        </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11646,12 +12540,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D449" t="n">
-        <v>-18000</v>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-18000,0</t>
+        </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11671,12 +12567,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D450" t="n">
-        <v>69810</v>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>69810,0</t>
+        </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11696,12 +12594,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D451" t="n">
-        <v>-69810</v>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>-69810,0</t>
+        </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11721,12 +12621,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D452" t="n">
-        <v>70.16</v>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>70,16</t>
+        </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11746,12 +12648,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D453" t="n">
-        <v>1103570.37</v>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>1103570,37</t>
+        </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11771,12 +12675,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D454" t="n">
-        <v>-130567.57</v>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-130567,57</t>
+        </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11796,12 +12702,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D455" t="n">
-        <v>132000</v>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>132000,0</t>
+        </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11821,12 +12729,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D456" t="n">
-        <v>-1111149.23</v>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>-1111149,23</t>
+        </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11846,12 +12756,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D457" t="n">
-        <v>17676.08</v>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>17676,08</t>
+        </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11871,12 +12783,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D458" t="n">
-        <v>270000.99</v>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>270000,99</t>
+        </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11896,12 +12810,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D459" t="n">
-        <v>-65000</v>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-65000,0</t>
+        </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11921,12 +12837,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D460" t="n">
-        <v>44251</v>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>44251,0</t>
+        </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11946,12 +12864,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D461" t="n">
-        <v>-44251</v>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>-44251,0</t>
+        </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11971,12 +12891,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D462" t="n">
-        <v>-20000</v>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>-20000,0</t>
+        </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -11996,12 +12918,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D463" t="n">
-        <v>-3025</v>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>-3025,0</t>
+        </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12021,12 +12945,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D464" t="n">
-        <v>3.23</v>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>3,23</t>
+        </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12046,12 +12972,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D465" t="n">
-        <v>-80000</v>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>-80000,0</t>
+        </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12999,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D466" t="n">
-        <v>-98096.95</v>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>-98096,95</t>
+        </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12096,12 +13026,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D467" t="n">
-        <v>8494.940000000001</v>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>8494,94</t>
+        </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12121,12 +13053,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D468" t="n">
-        <v>-8494.940000000001</v>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>-8494,94</t>
+        </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12146,12 +13080,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D469" t="n">
-        <v>-22000</v>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>-22000,0</t>
+        </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12171,12 +13107,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D470" t="n">
-        <v>11930.81</v>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>11930,81</t>
+        </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12196,12 +13134,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D471" t="n">
-        <v>-11930.81</v>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-11930,81</t>
+        </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12221,12 +13161,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D472" t="n">
-        <v>34.71</v>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>34,71</t>
+        </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12246,12 +13188,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D473" t="n">
-        <v>750276.5699999999</v>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>750276,57</t>
+        </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12271,12 +13215,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D474" t="n">
-        <v>-750000</v>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-750000,0</t>
+        </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12296,12 +13242,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D475" t="n">
-        <v>3.05</v>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>3,05</t>
+        </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12321,12 +13269,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D476" t="n">
-        <v>45000</v>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>45000,0</t>
+        </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12346,12 +13296,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D477" t="n">
-        <v>-42500</v>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>-42500,0</t>
+        </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12371,12 +13323,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D478" t="n">
-        <v>21000</v>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>21000,0</t>
+        </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12396,12 +13350,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D479" t="n">
-        <v>7.92</v>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>7,92</t>
+        </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
@@ -12421,12 +13377,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D480" t="n">
-        <v>-20000</v>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>-20000,0</t>
+        </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>mercadopago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
